--- a/docs/ราคาอลู-3แบรนด์-เทียบก่อนสลับ.xlsx
+++ b/docs/ราคาอลู-3แบรนด์-เทียบก่อนสลับ.xlsx
@@ -983,7 +983,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">JR03136</t>
+          <t xml:space="preserve">JR02944</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -993,27 +993,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">ฝาครอบรางบน</t>
-        </is>
-      </c>
-      <c r="D20">
-        <v>1</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">น้ำหนักที่ฝังในสูตร (ยังไม่ยืนยัน)</t>
+          <t xml:space="preserve">ฉากข้อต่อ 2" (เฉพาะแปะนอก)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcdoor</t>
+          <t xml:space="preserve">gate</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">JR03141</t>
+          <t xml:space="preserve">JR03136</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1023,7 +1015,15 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">รางบนบานเลื่อน Hafele</t>
+          <t xml:space="preserve">ฝาครอบรางบน</t>
+        </is>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">น้ำหนักที่ฝังในสูตร (ยังไม่ยืนยัน)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1035,7 +1035,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">OPK-A201-40</t>
+          <t xml:space="preserve">JR03141</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1045,27 +1045,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ขวางบน-ล่าง</t>
-        </is>
-      </c>
-      <c r="D22">
-        <v>4.69</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">น้ำหนักที่ฝังในสูตร (ยังไม่ยืนยัน)</t>
+          <t xml:space="preserve">รางบนบานเลื่อน Hafele</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">slimlux velora_auto</t>
+          <t xml:space="preserve">pcdoor</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">OPK-A202-40</t>
+          <t xml:space="preserve">OPK-A201-40</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1075,11 +1067,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">เสากุญแจ (ไส้เสาบาน)</t>
+          <t xml:space="preserve">ขวางบน-ล่าง</t>
         </is>
       </c>
       <c r="D23">
-        <v>2.95</v>
+        <v>4.69</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1095,7 +1087,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">OPK-A203-40</t>
+          <t xml:space="preserve">OPK-A202-40</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1105,11 +1097,11 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">ตบเรียบหน้าเสากุญแจ</t>
+          <t xml:space="preserve">เสากุญแจ (ไส้เสาบาน)</t>
         </is>
       </c>
       <c r="D24">
-        <v>1.57</v>
+        <v>2.95</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1125,7 +1117,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">OPK-A204-40</t>
+          <t xml:space="preserve">OPK-A203-40</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1135,11 +1127,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">ตบเกี่ยวใส่สักหลาด</t>
+          <t xml:space="preserve">ตบเรียบหน้าเสากุญแจ</t>
         </is>
       </c>
       <c r="D25">
-        <v>1.692</v>
+        <v>1.57</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1148,14 +1140,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">slimlux</t>
+          <t xml:space="preserve">slimlux velora_auto</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">XSW400013</t>
+          <t xml:space="preserve">OPK-A204-40</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1165,11 +1157,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">ตบปิดใต้รางริม (ฝาปิดล่างเล็ก)</t>
+          <t xml:space="preserve">ตบเกี่ยวใส่สักหลาด</t>
         </is>
       </c>
       <c r="D26">
-        <v>0.474</v>
+        <v>1.692</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1185,7 +1177,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">XSW400023</t>
+          <t xml:space="preserve">XSW400013</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1195,7 +1187,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">ตบปิดใต้รางกลาง (ฝาปิดล่างใหญ่)</t>
+          <t xml:space="preserve">ตบปิดใต้รางริม (ฝาปิดล่างเล็ก)</t>
         </is>
       </c>
       <c r="D27">
@@ -1215,7 +1207,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">XSW40008</t>
+          <t xml:space="preserve">XSW400023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1225,11 +1217,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">รางแขวน 1 ราง</t>
+          <t xml:space="preserve">ตบปิดใต้รางกลาง (ฝาปิดล่างใหญ่)</t>
         </is>
       </c>
       <c r="D28">
-        <v>5.46</v>
+        <v>0.474</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1245,40 +1237,37 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">กล่อง 1.6"x1.6"</t>
+          <t xml:space="preserve">XSW40008</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Euro Fuji</t>
+          <t xml:space="preserve">fixed</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">ใบระแนง A (กล่อง 1.6×1.6″)</t>
+          <t xml:space="preserve">รางแขวน 1 ราง</t>
         </is>
       </c>
       <c r="D29">
-        <v>2.27</v>
+        <v>5.46</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">เมืองทอง · ไม่มี 1.5/1.2 → ใช้ NaN มม. (หนาสุดที่มี) ⚠</t>
-        </is>
-      </c>
-      <c r="G29">
-        <v>438</v>
+          <t xml:space="preserve">น้ำหนักที่ฝังในสูตร (ยังไม่ยืนยัน)</t>
+        </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">gate roof roof_gable</t>
+          <t xml:space="preserve">slimlux</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">กล่อง 1.6"x3"</t>
+          <t xml:space="preserve">กล่อง 1.6"x1.6"</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1288,30 +1277,30 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">กล่อง 1.6×3 — ตั้ง</t>
+          <t xml:space="preserve">ใบระแนง A (กล่อง 1.6×1.6″)</t>
         </is>
       </c>
       <c r="D30">
-        <v>5.736</v>
+        <v>2.27</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">เมืองทอง · ไม่มี 1.5/1.2 → ใช้ 1.6 มม. (หนาสุดที่มี) ⚠</t>
+          <t xml:space="preserve">เมืองทอง · ไม่มี 1.5/1.2 → ใช้ NaN มม. (หนาสุดที่มี) ⚠</t>
         </is>
       </c>
       <c r="G30">
-        <v>1107</v>
+        <v>438</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">fixed</t>
+          <t xml:space="preserve">gate roof roof_gable</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">กล่อง 1.6"x4"</t>
+          <t xml:space="preserve">กล่อง 1.6"x3"</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1321,11 +1310,11 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">ใบระแนง A (กล่อง 1.6×4″)</t>
+          <t xml:space="preserve">กล่อง 1.6×3 — ตั้ง</t>
         </is>
       </c>
       <c r="D31">
-        <v>6.978</v>
+        <v>5.736</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1333,18 +1322,18 @@
         </is>
       </c>
       <c r="G31">
-        <v>1347</v>
+        <v>1107</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">gate roof roof_gable</t>
+          <t xml:space="preserve">fixed</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">กล่อง 1"x1"</t>
+          <t xml:space="preserve">กล่อง 1.6"x4"</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1354,30 +1343,30 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">ใบระแนง A (กล่อง 1×1″)</t>
+          <t xml:space="preserve">ใบระแนง A (กล่อง 1.6×4″)</t>
         </is>
       </c>
       <c r="D32">
-        <v>1.57</v>
+        <v>6.978</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">เมืองทอง · ไม่มี 1.5/1.2 → ใช้ NaN มม. (หนาสุดที่มี) ⚠</t>
+          <t xml:space="preserve">เมืองทอง · ไม่มี 1.5/1.2 → ใช้ 1.6 มม. (หนาสุดที่มี) ⚠</t>
         </is>
       </c>
       <c r="G32">
-        <v>303</v>
+        <v>1347</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">gate</t>
+          <t xml:space="preserve">gate roof roof_gable</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">กล่อง 1"x1.6"</t>
+          <t xml:space="preserve">กล่อง 1"x1"</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1387,11 +1376,11 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">ใบระแนง A (กล่อง 1×1.6″)</t>
+          <t xml:space="preserve">ใบระแนง A (กล่อง 1×1″)</t>
         </is>
       </c>
       <c r="D33">
-        <v>2.41</v>
+        <v>1.57</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1399,7 +1388,7 @@
         </is>
       </c>
       <c r="G33">
-        <v>465</v>
+        <v>303</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1410,7 +1399,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">กล่อง 1"x4"</t>
+          <t xml:space="preserve">กล่อง 1"x1.6"</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1420,11 +1409,11 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">คาน (กล่อง 1"x4")</t>
+          <t xml:space="preserve">ใบระแนง A (กล่อง 1×1.6″)</t>
         </is>
       </c>
       <c r="D34">
-        <v>4.86</v>
+        <v>2.41</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1432,18 +1421,18 @@
         </is>
       </c>
       <c r="G34">
-        <v>938</v>
+        <v>465</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">slimlux gate</t>
+          <t xml:space="preserve">gate</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">กล่อง 2"x4"</t>
+          <t xml:space="preserve">กล่อง 1"x4"</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1453,11 +1442,11 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">เสาตั้งข้าง (2×4)</t>
+          <t xml:space="preserve">คาน (กล่อง 1"x4")</t>
         </is>
       </c>
       <c r="D35">
-        <v>7.29</v>
+        <v>4.86</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1465,18 +1454,18 @@
         </is>
       </c>
       <c r="G35">
-        <v>1407</v>
+        <v>938</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">gate</t>
+          <t xml:space="preserve">slimlux gate</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">กล่อง 4"x4"</t>
+          <t xml:space="preserve">กล่อง 2"x4"</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1486,30 +1475,30 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">เสารับไกด์ (4×4) — เสาแยก</t>
+          <t xml:space="preserve">เสาตั้งข้าง (2×4)</t>
         </is>
       </c>
       <c r="D36">
-        <v>12.954</v>
+        <v>7.29</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">เมืองทอง · ไม่มี 1.5/1.2 → ใช้ 4 มม. (หนาสุดที่มี) ⚠</t>
+          <t xml:space="preserve">เมืองทอง · ไม่มี 1.5/1.2 → ใช้ NaN มม. (หนาสุดที่มี) ⚠</t>
         </is>
       </c>
       <c r="G36">
-        <v>2500</v>
+        <v>1407</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">gate roof_gable</t>
+          <t xml:space="preserve">gate</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">ฉาก 2"</t>
+          <t xml:space="preserve">กล่อง 4"x4"</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1519,30 +1508,30 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">ฉากปิดราง 2"</t>
+          <t xml:space="preserve">เสารับไกด์ (4×4) — เสาแยก</t>
         </is>
       </c>
       <c r="D37">
-        <v>1.63</v>
+        <v>12.954</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">น้ำหนักที่ฝังในสูตร (ยังไม่ยืนยัน)</t>
+          <t xml:space="preserve">เมืองทอง · ไม่มี 1.5/1.2 → ใช้ 4 มม. (หนาสุดที่มี) ⚠</t>
         </is>
       </c>
       <c r="G37">
-        <v>315</v>
+        <v>2500</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">slimlux</t>
+          <t xml:space="preserve">gate roof_gable</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">ฉาก 6 หุน</t>
+          <t xml:space="preserve">ฉาก 2"</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1552,30 +1541,30 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">ฉาก 6 หุน</t>
+          <t xml:space="preserve">ฉากปิดราง 2"</t>
         </is>
       </c>
       <c r="D38">
-        <v>1</v>
+        <v>1.63</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">ไฟล์น้ำหนักโปรไฟล์</t>
+          <t xml:space="preserve">น้ำหนักที่ฝังในสูตร (ยังไม่ยืนยัน)</t>
         </is>
       </c>
       <c r="G38">
-        <v>193</v>
+        <v>315</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">roof roof_gable</t>
+          <t xml:space="preserve">slimlux</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7852</t>
+          <t xml:space="preserve">ฉาก 4"</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1585,38 +1574,19 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">ตบเฟรมแบ่งบาน F7852</t>
-        </is>
-      </c>
-      <c r="D39">
-        <v>4.397</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ไฟล์น้ำหนักโปรไฟล์</t>
-        </is>
-      </c>
-      <c r="F39">
-        <v>789.5</v>
-      </c>
-      <c r="G39">
-        <v>849</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8%</t>
+          <t xml:space="preserve">ฉาก 4" ปิดราง</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">open_door</t>
+          <t xml:space="preserve">topslide</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7854</t>
+          <t xml:space="preserve">ฉาก 6 หุน</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1626,38 +1596,30 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">เฟรมแบ่งบาน F7854</t>
+          <t xml:space="preserve">ฉาก 6 หุน</t>
         </is>
       </c>
       <c r="D40">
-        <v>7.642</v>
+        <v>1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
           <t xml:space="preserve">ไฟล์น้ำหนักโปรไฟล์</t>
         </is>
       </c>
-      <c r="F40">
-        <v>1371.3</v>
-      </c>
       <c r="G40">
-        <v>1475</v>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8%</t>
-        </is>
+        <v>193</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">open_door</t>
+          <t xml:space="preserve">roof roof_gable</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7855</t>
+          <t xml:space="preserve">F7852</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1667,11 +1629,11 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">ชนกลางรับแรง F7855</t>
+          <t xml:space="preserve">ตบเฟรมแบ่งบาน F7852</t>
         </is>
       </c>
       <c r="D41">
-        <v>7.149</v>
+        <v>4.397</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1679,26 +1641,26 @@
         </is>
       </c>
       <c r="F41">
-        <v>1300</v>
+        <v>789.5</v>
       </c>
       <c r="G41">
-        <v>1380</v>
+        <v>849</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">6%</t>
+          <t xml:space="preserve">8%</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">euro_slide</t>
+          <t xml:space="preserve">open_door</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7859</t>
+          <t xml:space="preserve">F7854</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1708,11 +1670,11 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">เฟรมข้าง F7859</t>
+          <t xml:space="preserve">เฟรมแบ่งบาน F7854</t>
         </is>
       </c>
       <c r="D42">
-        <v>5.984</v>
+        <v>7.642</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1720,26 +1682,26 @@
         </is>
       </c>
       <c r="F42">
-        <v>1205</v>
+        <v>1371.3</v>
       </c>
       <c r="G42">
-        <v>1155</v>
+        <v>1475</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">-4%</t>
+          <t xml:space="preserve">8%</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">open_door awning pivot bansolid</t>
+          <t xml:space="preserve">open_door</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7863</t>
+          <t xml:space="preserve">F7855</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1749,11 +1711,11 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">ชายล่าง F7863</t>
+          <t xml:space="preserve">ชนกลางรับแรง F7855</t>
         </is>
       </c>
       <c r="D43">
-        <v>2.202</v>
+        <v>7.149</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1761,26 +1723,26 @@
         </is>
       </c>
       <c r="F43">
-        <v>435</v>
+        <v>1300</v>
       </c>
       <c r="G43">
-        <v>425</v>
+        <v>1380</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">-2%</t>
+          <t xml:space="preserve">6%</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">open_door pivot bansolid</t>
+          <t xml:space="preserve">euro_slide</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7864</t>
+          <t xml:space="preserve">F7859</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1790,38 +1752,38 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">เสา (กรอบบาน 10 ซม.)</t>
+          <t xml:space="preserve">เฟรมข้าง F7859</t>
         </is>
       </c>
       <c r="D44">
-        <v>11.328</v>
+        <v>6.63</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">น้ำหนักที่ฝังในสูตร (ยังไม่ยืนยัน)</t>
+          <t xml:space="preserve">ไฟล์น้ำหนักโปรไฟล์</t>
         </is>
       </c>
       <c r="F44">
-        <v>2165</v>
+        <v>1205</v>
       </c>
       <c r="G44">
-        <v>2186</v>
+        <v>1280</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">1%</t>
+          <t xml:space="preserve">6%</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">open_door pivot bansolid</t>
+          <t xml:space="preserve">open_door awning pivot bansolid</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7869</t>
+          <t xml:space="preserve">F7863</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1831,11 +1793,11 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">เฟรมบน</t>
+          <t xml:space="preserve">ชายล่าง F7863</t>
         </is>
       </c>
       <c r="D45">
-        <v>14.963</v>
+        <v>2.202</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1843,26 +1805,26 @@
         </is>
       </c>
       <c r="F45">
-        <v>2765</v>
+        <v>435</v>
       </c>
       <c r="G45">
-        <v>2888</v>
+        <v>425</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">4%</t>
+          <t xml:space="preserve">-2%</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">euro_slide</t>
+          <t xml:space="preserve">open_door pivot bansolid</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7879</t>
+          <t xml:space="preserve">F7864</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1872,11 +1834,11 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">ตบปิดเฟรมร่องกลาง</t>
+          <t xml:space="preserve">เสา (กรอบบาน 10 ซม.)</t>
         </is>
       </c>
       <c r="D46">
-        <v>1.888</v>
+        <v>11.328</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1884,26 +1846,26 @@
         </is>
       </c>
       <c r="F46">
-        <v>375</v>
+        <v>2165</v>
       </c>
       <c r="G46">
-        <v>364</v>
+        <v>2186</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">-3%</t>
+          <t xml:space="preserve">1%</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">euro_slide</t>
+          <t xml:space="preserve">open_door pivot bansolid</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7880</t>
+          <t xml:space="preserve">F7869</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1913,11 +1875,11 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">ตบปิดเฟรมร่องใน</t>
+          <t xml:space="preserve">เฟรมบน</t>
         </is>
       </c>
       <c r="D47">
-        <v>1.869</v>
+        <v>14.963</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1925,14 +1887,14 @@
         </is>
       </c>
       <c r="F47">
-        <v>370</v>
+        <v>2765</v>
       </c>
       <c r="G47">
-        <v>361</v>
+        <v>2888</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">-2%</t>
+          <t xml:space="preserve">4%</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -1944,7 +1906,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7902</t>
+          <t xml:space="preserve">F7879</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1954,11 +1916,11 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">เฟรมล่าง (งานใน ตัวเตี้ย)</t>
+          <t xml:space="preserve">ตบปิดเฟรมร่องกลาง</t>
         </is>
       </c>
       <c r="D48">
-        <v>6.586</v>
+        <v>1.888</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1966,14 +1928,14 @@
         </is>
       </c>
       <c r="F48">
-        <v>1220</v>
+        <v>375</v>
       </c>
       <c r="G48">
-        <v>1271</v>
+        <v>364</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">4%</t>
+          <t xml:space="preserve">-3%</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -1985,7 +1947,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7917</t>
+          <t xml:space="preserve">F7880</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1995,11 +1957,11 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">คิ้ว ตั้ง</t>
+          <t xml:space="preserve">ตบปิดเฟรมร่องใน</t>
         </is>
       </c>
       <c r="D49">
-        <v>0.794</v>
+        <v>1.869</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2007,14 +1969,14 @@
         </is>
       </c>
       <c r="F49">
-        <v>166.2</v>
+        <v>370</v>
       </c>
       <c r="G49">
-        <v>153</v>
+        <v>361</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">-8%</t>
+          <t xml:space="preserve">-2%</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2026,7 +1988,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7919</t>
+          <t xml:space="preserve">F7902</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2036,11 +1998,11 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">คิ้ว ตั้ง</t>
+          <t xml:space="preserve">เฟรมล่าง (งานใน ตัวเตี้ย)</t>
         </is>
       </c>
       <c r="D50">
-        <v>1.05</v>
+        <v>6.586</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2048,14 +2010,14 @@
         </is>
       </c>
       <c r="F50">
-        <v>220</v>
+        <v>1220</v>
       </c>
       <c r="G50">
-        <v>203</v>
+        <v>1271</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">-8%</t>
+          <t xml:space="preserve">4%</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2067,7 +2029,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7925</t>
+          <t xml:space="preserve">F7917</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2077,11 +2039,11 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">ต่อชนกลาง F7925</t>
+          <t xml:space="preserve">คิ้ว ตั้ง</t>
         </is>
       </c>
       <c r="D51">
-        <v>2.163</v>
+        <v>0.794</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2089,14 +2051,14 @@
         </is>
       </c>
       <c r="F51">
-        <v>410.3</v>
+        <v>166.2</v>
       </c>
       <c r="G51">
-        <v>417</v>
+        <v>153</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2%</t>
+          <t xml:space="preserve">-8%</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2108,7 +2070,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7932</t>
+          <t xml:space="preserve">F7919</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2118,11 +2080,11 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">เฟรมล่าง/รางยู</t>
+          <t xml:space="preserve">คิ้ว ตั้ง</t>
         </is>
       </c>
       <c r="D52">
-        <v>1.939</v>
+        <v>1.05</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2130,10 +2092,10 @@
         </is>
       </c>
       <c r="F52">
-        <v>405.2</v>
+        <v>220</v>
       </c>
       <c r="G52">
-        <v>374</v>
+        <v>203</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2142,14 +2104,14 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">fold_euro</t>
+          <t xml:space="preserve">euro_slide</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7935</t>
+          <t xml:space="preserve">F7925</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2159,11 +2121,11 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">คิ้วตั้ง F7935</t>
+          <t xml:space="preserve">ต่อชนกลาง F7925</t>
         </is>
       </c>
       <c r="D53">
-        <v>1.824</v>
+        <v>2.163</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2171,26 +2133,26 @@
         </is>
       </c>
       <c r="F53">
-        <v>380</v>
+        <v>410.3</v>
       </c>
       <c r="G53">
-        <v>352</v>
+        <v>417</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">-7%</t>
+          <t xml:space="preserve">2%</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">open_door awning fold_euro pivot fold_li</t>
+          <t xml:space="preserve">euro_slide</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7937</t>
+          <t xml:space="preserve">F7932</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2200,11 +2162,11 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">เฟรมข้างช่องแสง F7937</t>
+          <t xml:space="preserve">เฟรมล่าง/รางยู</t>
         </is>
       </c>
       <c r="D54">
-        <v>7.053</v>
+        <v>1.939</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2212,26 +2174,26 @@
         </is>
       </c>
       <c r="F54">
-        <v>1226</v>
+        <v>405.2</v>
       </c>
       <c r="G54">
-        <v>1361</v>
+        <v>374</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">11%</t>
+          <t xml:space="preserve">-8%</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">open_door</t>
+          <t xml:space="preserve">fold_euro</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7938B</t>
+          <t xml:space="preserve">F7935</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2241,11 +2203,11 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">เฟรมล่าง (ธรณี) F7938B</t>
+          <t xml:space="preserve">คิ้วตั้ง F7935</t>
         </is>
       </c>
       <c r="D55">
-        <v>7.629</v>
+        <v>1.824</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2253,26 +2215,26 @@
         </is>
       </c>
       <c r="F55">
-        <v>1520</v>
+        <v>380</v>
       </c>
       <c r="G55">
-        <v>1472</v>
+        <v>352</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">-3%</t>
+          <t xml:space="preserve">-7%</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">open_door pivot bansolid</t>
+          <t xml:space="preserve">open_door awning fold_euro pivot fold_li</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7939</t>
+          <t xml:space="preserve">F7937</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2282,19 +2244,27 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">เฟรมข้าง F7939 (มีช่องแสงล่าง)</t>
+          <t xml:space="preserve">เฟรมข้างช่องแสง F7937</t>
         </is>
       </c>
       <c r="D56">
-        <v>7.778</v>
+        <v>7.053</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">น้ำหนักที่ฝังในสูตร (ยังไม่ยืนยัน)</t>
-        </is>
+          <t xml:space="preserve">ไฟล์น้ำหนักโปรไฟล์</t>
+        </is>
+      </c>
+      <c r="F56">
+        <v>1226</v>
       </c>
       <c r="G56">
-        <v>1501</v>
+        <v>1361</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11%</t>
+        </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -2305,7 +2275,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7939B</t>
+          <t xml:space="preserve">F7938B</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2315,11 +2285,11 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">ธรณี F7939B</t>
+          <t xml:space="preserve">เฟรมล่าง (ธรณี) F7938B</t>
         </is>
       </c>
       <c r="D57">
-        <v>7.366</v>
+        <v>7.629</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2327,26 +2297,26 @@
         </is>
       </c>
       <c r="F57">
-        <v>1475</v>
+        <v>1520</v>
       </c>
       <c r="G57">
-        <v>1422</v>
+        <v>1472</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">-4%</t>
+          <t xml:space="preserve">-3%</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">awning</t>
+          <t xml:space="preserve">open_door pivot bansolid</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7943</t>
+          <t xml:space="preserve">F7939</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2356,11 +2326,11 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">เสา (กรอบบาน 8 ซม.)</t>
+          <t xml:space="preserve">เฟรมข้าง F7939 (มีช่องแสงล่าง)</t>
         </is>
       </c>
       <c r="D58">
-        <v>7.546</v>
+        <v>7.778</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2368,7 +2338,7 @@
         </is>
       </c>
       <c r="G58">
-        <v>1456</v>
+        <v>1501</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -2379,7 +2349,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7943B</t>
+          <t xml:space="preserve">F7939B</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2389,11 +2359,11 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">กรอบบาน เสา F7943B</t>
+          <t xml:space="preserve">ธรณี F7939B</t>
         </is>
       </c>
       <c r="D59">
-        <v>7.546</v>
+        <v>8.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2401,14 +2371,14 @@
         </is>
       </c>
       <c r="F59">
-        <v>1510</v>
+        <v>1475</v>
       </c>
       <c r="G59">
-        <v>1456</v>
+        <v>1563</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">-4%</t>
+          <t xml:space="preserve">6%</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -2420,7 +2390,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7944</t>
+          <t xml:space="preserve">F7943</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2430,11 +2400,11 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">เสามุ้ง F7944</t>
+          <t xml:space="preserve">เสา (กรอบบาน 8 ซม.)</t>
         </is>
       </c>
       <c r="D60">
-        <v>5</v>
+        <v>7.546</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2442,7 +2412,7 @@
         </is>
       </c>
       <c r="G60">
-        <v>965</v>
+        <v>1456</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -2453,7 +2423,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7945C</t>
+          <t xml:space="preserve">F7943B</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2463,11 +2433,11 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">ชนกลาง F7945C</t>
+          <t xml:space="preserve">กรอบบาน เสา F7943B</t>
         </is>
       </c>
       <c r="D61">
-        <v>3.795</v>
+        <v>7.546</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2475,26 +2445,26 @@
         </is>
       </c>
       <c r="F61">
-        <v>820</v>
+        <v>1510</v>
       </c>
       <c r="G61">
-        <v>732</v>
+        <v>1456</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">-11%</t>
+          <t xml:space="preserve">-4%</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">open_door awning pivot bansolid</t>
+          <t xml:space="preserve">awning</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7949</t>
+          <t xml:space="preserve">F7944</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2504,30 +2474,30 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">คิ้วกระจก (ตั้ง)</t>
+          <t xml:space="preserve">เสามุ้ง F7944</t>
         </is>
       </c>
       <c r="D62">
-        <v>1.613</v>
+        <v>5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">ไฟล์น้ำหนักโปรไฟล์</t>
+          <t xml:space="preserve">น้ำหนักที่ฝังในสูตร (ยังไม่ยืนยัน)</t>
         </is>
       </c>
       <c r="G62">
-        <v>311</v>
+        <v>965</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">fold_euro</t>
+          <t xml:space="preserve">open_door</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7951</t>
+          <t xml:space="preserve">F7945C</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2537,11 +2507,11 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">เสารับแรง (สูงเกิน 2.8 ม.)</t>
+          <t xml:space="preserve">ชนกลาง F7945C</t>
         </is>
       </c>
       <c r="D63">
-        <v>11.533</v>
+        <v>3.795</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2549,26 +2519,26 @@
         </is>
       </c>
       <c r="F63">
-        <v>2175</v>
+        <v>820</v>
       </c>
       <c r="G63">
-        <v>2226</v>
+        <v>732</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2%</t>
+          <t xml:space="preserve">-11%</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">euro_slide</t>
+          <t xml:space="preserve">open_door awning pivot bansolid</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7960</t>
+          <t xml:space="preserve">F7949</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2578,38 +2548,30 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">ตบธรณี F7960</t>
+          <t xml:space="preserve">คิ้วกระจก (ตั้ง)</t>
         </is>
       </c>
       <c r="D64">
-        <v>3.123</v>
+        <v>1.613</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
           <t xml:space="preserve">ไฟล์น้ำหนักโปรไฟล์</t>
         </is>
       </c>
-      <c r="F64">
-        <v>610</v>
-      </c>
       <c r="G64">
-        <v>603</v>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-1%</t>
-        </is>
+        <v>311</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">open_door pivot bansolid</t>
+          <t xml:space="preserve">fold_euro</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7961</t>
+          <t xml:space="preserve">F7951</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2619,11 +2581,11 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7961 รับล็อคเฟรมข้างบานคู่</t>
+          <t xml:space="preserve">เสารับแรง (สูงเกิน 2.8 ม.)</t>
         </is>
       </c>
       <c r="D65">
-        <v>3.174</v>
+        <v>11.533</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2631,26 +2593,26 @@
         </is>
       </c>
       <c r="F65">
-        <v>613</v>
+        <v>2175</v>
       </c>
       <c r="G65">
-        <v>613</v>
+        <v>2226</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">0%</t>
+          <t xml:space="preserve">2%</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">fold_euro</t>
+          <t xml:space="preserve">euro_slide</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7962</t>
+          <t xml:space="preserve">F7960</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2660,11 +2622,11 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7962 รับล็อคบานคู่+บานคี่</t>
+          <t xml:space="preserve">ตบธรณี F7960</t>
         </is>
       </c>
       <c r="D66">
-        <v>5.594</v>
+        <v>3.123</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2672,26 +2634,26 @@
         </is>
       </c>
       <c r="F66">
-        <v>1035</v>
+        <v>610</v>
       </c>
       <c r="G66">
-        <v>1080</v>
+        <v>603</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">4%</t>
+          <t xml:space="preserve">-1%</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">fold_euro</t>
+          <t xml:space="preserve">open_door pivot bansolid</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7968</t>
+          <t xml:space="preserve">F7961</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2701,11 +2663,11 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7968 เฟรมบนบานเฟี้ยม</t>
+          <t xml:space="preserve">F7961 รับล็อคเฟรมข้างบานคู่</t>
         </is>
       </c>
       <c r="D67">
-        <v>17.709</v>
+        <v>3.174</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2713,10 +2675,10 @@
         </is>
       </c>
       <c r="F67">
-        <v>3415</v>
+        <v>613</v>
       </c>
       <c r="G67">
-        <v>3418</v>
+        <v>613</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -2725,14 +2687,14 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">fold_euro fold_lift</t>
+          <t xml:space="preserve">fold_euro</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7969</t>
+          <t xml:space="preserve">F7962</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2742,11 +2704,11 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">เฟรมล่าง/รางยู</t>
+          <t xml:space="preserve">F7962 รับล็อคบานคู่+บานคี่</t>
         </is>
       </c>
       <c r="D68">
-        <v>9.811</v>
+        <v>5.594</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2754,26 +2716,26 @@
         </is>
       </c>
       <c r="F68">
-        <v>1895</v>
+        <v>1035</v>
       </c>
       <c r="G68">
-        <v>1894</v>
+        <v>1080</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">0%</t>
+          <t xml:space="preserve">4%</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">fold_euro fold_lift</t>
+          <t xml:space="preserve">fold_euro</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7970</t>
+          <t xml:space="preserve">F7968</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2783,11 +2745,11 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7970 เฟรมข้างบานเฟี้ยม</t>
+          <t xml:space="preserve">F7968 เฟรมบนบานเฟี้ยม</t>
         </is>
       </c>
       <c r="D69">
-        <v>5.978</v>
+        <v>17.709</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2795,14 +2757,14 @@
         </is>
       </c>
       <c r="F69">
-        <v>1120</v>
+        <v>3415</v>
       </c>
       <c r="G69">
-        <v>1154</v>
+        <v>3418</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">3%</t>
+          <t xml:space="preserve">0%</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -2814,7 +2776,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7971</t>
+          <t xml:space="preserve">F7969</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2824,11 +2786,11 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7971 คิ้วตบเฟรมข้าง</t>
+          <t xml:space="preserve">เฟรมล่าง/รางยู</t>
         </is>
       </c>
       <c r="D70">
-        <v>2.56</v>
+        <v>9.811</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2836,14 +2798,14 @@
         </is>
       </c>
       <c r="F70">
-        <v>520</v>
+        <v>1895</v>
       </c>
       <c r="G70">
-        <v>494</v>
+        <v>1894</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">-5%</t>
+          <t xml:space="preserve">0%</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -2855,7 +2817,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7972</t>
+          <t xml:space="preserve">F7970</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2865,11 +2827,11 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7972 กรอบบานเฟี้ยม (ตั้ง)</t>
+          <t xml:space="preserve">F7970 เฟรมข้างบานเฟี้ยม</t>
         </is>
       </c>
       <c r="D71">
-        <v>9.542</v>
+        <v>5.978</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2877,14 +2839,14 @@
         </is>
       </c>
       <c r="F71">
-        <v>1885</v>
+        <v>1120</v>
       </c>
       <c r="G71">
-        <v>1842</v>
+        <v>1154</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">-2%</t>
+          <t xml:space="preserve">3%</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -2896,7 +2858,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7973</t>
+          <t xml:space="preserve">F7971</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2906,11 +2868,11 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7973 ตบปิดเฟรม (ตั้ง)</t>
+          <t xml:space="preserve">F7971 คิ้วตบเฟรมข้าง</t>
         </is>
       </c>
       <c r="D72">
-        <v>1.216</v>
+        <v>2.56</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2918,14 +2880,14 @@
         </is>
       </c>
       <c r="F72">
-        <v>245</v>
+        <v>520</v>
       </c>
       <c r="G72">
-        <v>235</v>
+        <v>494</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">-4%</t>
+          <t xml:space="preserve">-5%</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -2937,7 +2899,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7974</t>
+          <t xml:space="preserve">F7972</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2947,11 +2909,11 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7974 ชนกลางบานคู่</t>
+          <t xml:space="preserve">F7972 กรอบบานเฟี้ยม (ตั้ง)</t>
         </is>
       </c>
       <c r="D73">
-        <v>5.114</v>
+        <v>9.542</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2959,26 +2921,26 @@
         </is>
       </c>
       <c r="F73">
-        <v>1000</v>
+        <v>1885</v>
       </c>
       <c r="G73">
-        <v>987</v>
+        <v>1842</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">-1%</t>
+          <t xml:space="preserve">-2%</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">fold_euro</t>
+          <t xml:space="preserve">fold_euro fold_lift</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7975</t>
+          <t xml:space="preserve">F7973</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2988,11 +2950,11 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7975 บังใบ</t>
+          <t xml:space="preserve">F7973 ตบปิดเฟรม (ตั้ง)</t>
         </is>
       </c>
       <c r="D74">
-        <v>2.893</v>
+        <v>1.216</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -3000,26 +2962,26 @@
         </is>
       </c>
       <c r="F74">
-        <v>561</v>
+        <v>245</v>
       </c>
       <c r="G74">
-        <v>558</v>
+        <v>235</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">-1%</t>
+          <t xml:space="preserve">-4%</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">fold_euro</t>
+          <t xml:space="preserve">fold_euro fold_lift</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7978</t>
+          <t xml:space="preserve">F7974</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3029,11 +2991,11 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">เฟรมข้าง</t>
+          <t xml:space="preserve">F7974 ชนกลางบานคู่</t>
         </is>
       </c>
       <c r="D75">
-        <v>4.902</v>
+        <v>5.114</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -3041,26 +3003,26 @@
         </is>
       </c>
       <c r="F75">
-        <v>1005</v>
+        <v>1000</v>
       </c>
       <c r="G75">
-        <v>946</v>
+        <v>987</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">-6%</t>
+          <t xml:space="preserve">-1%</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">euro_slide</t>
+          <t xml:space="preserve">fold_euro</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7979</t>
+          <t xml:space="preserve">F7975</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3070,11 +3032,11 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">เฟรมข้าง (2 ราง)</t>
+          <t xml:space="preserve">F7975 บังใบ</t>
         </is>
       </c>
       <c r="D76">
-        <v>3.514</v>
+        <v>2.893</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -3082,26 +3044,26 @@
         </is>
       </c>
       <c r="F76">
-        <v>690</v>
+        <v>561</v>
       </c>
       <c r="G76">
-        <v>678</v>
+        <v>558</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">-2%</t>
+          <t xml:space="preserve">-1%</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">euro_slide</t>
+          <t xml:space="preserve">fold_euro</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7980</t>
+          <t xml:space="preserve">F7978</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3111,11 +3073,11 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">เสา</t>
+          <t xml:space="preserve">เฟรมข้าง</t>
         </is>
       </c>
       <c r="D77">
-        <v>7.814</v>
+        <v>4.902</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -3123,14 +3085,14 @@
         </is>
       </c>
       <c r="F77">
-        <v>1530</v>
+        <v>1005</v>
       </c>
       <c r="G77">
-        <v>1508</v>
+        <v>946</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">-1%</t>
+          <t xml:space="preserve">-6%</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3142,7 +3104,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7983</t>
+          <t xml:space="preserve">F7979</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3152,11 +3114,11 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">ตบเกี่ยว</t>
+          <t xml:space="preserve">เฟรมข้าง (2 ราง)</t>
         </is>
       </c>
       <c r="D78">
-        <v>2.451</v>
+        <v>3.514</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -3164,14 +3126,14 @@
         </is>
       </c>
       <c r="F78">
-        <v>520</v>
+        <v>690</v>
       </c>
       <c r="G78">
-        <v>473</v>
+        <v>678</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">-9%</t>
+          <t xml:space="preserve">-2%</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3183,7 +3145,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7986</t>
+          <t xml:space="preserve">F7980</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3193,11 +3155,11 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">เดือย (ยูข้าง)</t>
+          <t xml:space="preserve">เสา</t>
         </is>
       </c>
       <c r="D79">
-        <v>1.37</v>
+        <v>7.814</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -3205,14 +3167,14 @@
         </is>
       </c>
       <c r="F79">
-        <v>300</v>
+        <v>1530</v>
       </c>
       <c r="G79">
-        <v>264</v>
+        <v>1508</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">-12%</t>
+          <t xml:space="preserve">-1%</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3224,7 +3186,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7988</t>
+          <t xml:space="preserve">F7983</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3234,11 +3196,11 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">ตบยูข้าง (F7988)</t>
+          <t xml:space="preserve">ตบเกี่ยว</t>
         </is>
       </c>
       <c r="D80">
-        <v>0.307</v>
+        <v>2.451</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -3246,14 +3208,14 @@
         </is>
       </c>
       <c r="F80">
-        <v>100</v>
+        <v>520</v>
       </c>
       <c r="G80">
-        <v>59</v>
+        <v>473</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">-41%</t>
+          <t xml:space="preserve">-9%</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -3265,7 +3227,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7989</t>
+          <t xml:space="preserve">F7986</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3275,11 +3237,11 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">ต่อเฟรมข้าง</t>
+          <t xml:space="preserve">เดือย (ยูข้าง)</t>
         </is>
       </c>
       <c r="D81">
-        <v>1.606</v>
+        <v>1.37</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3287,14 +3249,14 @@
         </is>
       </c>
       <c r="F81">
-        <v>335</v>
+        <v>300</v>
       </c>
       <c r="G81">
-        <v>310</v>
+        <v>264</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">-7%</t>
+          <t xml:space="preserve">-12%</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -3306,7 +3268,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7990</t>
+          <t xml:space="preserve">F7988</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3316,11 +3278,11 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">ต่อราง</t>
+          <t xml:space="preserve">ตบยูข้าง (F7988)</t>
         </is>
       </c>
       <c r="D82">
-        <v>5.235</v>
+        <v>0.307</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3328,14 +3290,14 @@
         </is>
       </c>
       <c r="F82">
-        <v>1030</v>
+        <v>100</v>
       </c>
       <c r="G82">
-        <v>1010</v>
+        <v>59</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">-2%</t>
+          <t xml:space="preserve">-41%</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -3347,7 +3309,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7992</t>
+          <t xml:space="preserve">F7989</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3357,11 +3319,11 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">ตบปิดร่องบน (ตบกันสาด + ตัวปิด)</t>
+          <t xml:space="preserve">ต่อเฟรมข้าง</t>
         </is>
       </c>
       <c r="D83">
-        <v>2.694</v>
+        <v>1.606</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3369,14 +3331,14 @@
         </is>
       </c>
       <c r="F83">
-        <v>535</v>
+        <v>335</v>
       </c>
       <c r="G83">
-        <v>520</v>
+        <v>310</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">-3%</t>
+          <t xml:space="preserve">-7%</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -3388,7 +3350,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7993</t>
+          <t xml:space="preserve">F7990</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3398,11 +3360,11 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">ตบปิดราง F7993</t>
+          <t xml:space="preserve">ต่อราง</t>
         </is>
       </c>
       <c r="D84">
-        <v>0.314</v>
+        <v>5.235</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3410,14 +3372,14 @@
         </is>
       </c>
       <c r="F84">
-        <v>95</v>
+        <v>1030</v>
       </c>
       <c r="G84">
-        <v>61</v>
+        <v>1010</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">-36%</t>
+          <t xml:space="preserve">-2%</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -3429,7 +3391,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7994</t>
+          <t xml:space="preserve">F7992</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3439,11 +3401,11 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">ตบรางล้อ (รางนอก)</t>
+          <t xml:space="preserve">ตบปิดร่องบน (ตบกันสาด + ตัวปิด)</t>
         </is>
       </c>
       <c r="D85">
-        <v>0.531</v>
+        <v>2.694</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3451,26 +3413,26 @@
         </is>
       </c>
       <c r="F85">
-        <v>150</v>
+        <v>535</v>
       </c>
       <c r="G85">
-        <v>102</v>
+        <v>520</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">-32%</t>
+          <t xml:space="preserve">-3%</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">sms_slide euro_slide</t>
+          <t xml:space="preserve">euro_slide</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7997</t>
+          <t xml:space="preserve">F7993</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3480,11 +3442,11 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">กล่องก้านสลับ F7997</t>
+          <t xml:space="preserve">ตบปิดราง F7993</t>
         </is>
       </c>
       <c r="D86">
-        <v>9.338</v>
+        <v>0.314</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3492,26 +3454,26 @@
         </is>
       </c>
       <c r="F86">
-        <v>1745.3</v>
+        <v>95</v>
       </c>
       <c r="G86">
-        <v>1802</v>
+        <v>61</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">3%</t>
+          <t xml:space="preserve">-36%</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">open_door</t>
+          <t xml:space="preserve">euro_slide</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t xml:space="preserve">JR01949</t>
+          <t xml:space="preserve">F7994</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3521,19 +3483,38 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">ฉาก 4" ปิดราง</t>
+          <t xml:space="preserve">ตบรางล้อ (รางนอก)</t>
+        </is>
+      </c>
+      <c r="D87">
+        <v>0.531</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ไฟล์น้ำหนักโปรไฟล์</t>
+        </is>
+      </c>
+      <c r="F87">
+        <v>150</v>
+      </c>
+      <c r="G87">
+        <v>102</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-32%</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">topslide</t>
+          <t xml:space="preserve">sms_slide euro_slide</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t xml:space="preserve">JR01994</t>
+          <t xml:space="preserve">F7997</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3543,38 +3524,38 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">ลูกฟูก 2 ทาง แนวตั้ง (ยัดในช่อง)</t>
+          <t xml:space="preserve">กล่องก้านสลับ F7997</t>
         </is>
       </c>
       <c r="D88">
-        <v>2.544</v>
+        <v>9.338</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">ชีตน้ำหนักโปรไฟล์ แถว 53 (SlimLux · ลูกฟูก 6 ม. 0.424 กก./ม.)</t>
+          <t xml:space="preserve">ไฟล์น้ำหนักโปรไฟล์</t>
         </is>
       </c>
       <c r="F88">
-        <v>432</v>
+        <v>1745.3</v>
       </c>
       <c r="G88">
-        <v>491</v>
+        <v>1802</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">14%</t>
+          <t xml:space="preserve">3%</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">velora bansolid</t>
+          <t xml:space="preserve">open_door</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t xml:space="preserve">JR02892</t>
+          <t xml:space="preserve">JR01994</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3584,30 +3565,38 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve">กันสาด F7948</t>
+          <t xml:space="preserve">ลูกฟูก 2 ทาง แนวตั้ง (ยัดในช่อง)</t>
         </is>
       </c>
       <c r="D89">
-        <v>0.902</v>
+        <v>2.544</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">น้ำหนักที่ฝังในสูตร (ยังไม่ยืนยัน)</t>
-        </is>
+          <t xml:space="preserve">ชีตน้ำหนักโปรไฟล์ แถว 53 (SlimLux · ลูกฟูก 6 ม. 0.424 กก./ม.)</t>
+        </is>
+      </c>
+      <c r="F89">
+        <v>432</v>
       </c>
       <c r="G89">
-        <v>174</v>
+        <v>491</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14%</t>
+        </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">open_door</t>
+          <t xml:space="preserve">velora bansolid</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t xml:space="preserve">JR02893</t>
+          <t xml:space="preserve">JR02892</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3617,11 +3606,11 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">คิ้วมุ้งตั้ง F7949</t>
+          <t xml:space="preserve">กันสาด F7948</t>
         </is>
       </c>
       <c r="D90">
-        <v>1.613</v>
+        <v>0.902</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3629,7 +3618,7 @@
         </is>
       </c>
       <c r="G90">
-        <v>311</v>
+        <v>174</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -3640,7 +3629,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">JR02894</t>
+          <t xml:space="preserve">JR02893</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3650,11 +3639,11 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">ตบนอกในบานตาย F7860</t>
+          <t xml:space="preserve">คิ้วมุ้งตั้ง F7949</t>
         </is>
       </c>
       <c r="D91">
-        <v>2.637</v>
+        <v>1.613</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3662,7 +3651,7 @@
         </is>
       </c>
       <c r="G91">
-        <v>509</v>
+        <v>311</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -3673,51 +3662,62 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve">JR01984</t>
+          <t xml:space="preserve">JR02894</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t xml:space="preserve">?</t>
+          <t xml:space="preserve">Euro Fuji</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t xml:space="preserve">กล่องเรียบ 1.6"×4" แนวตั้ง (ครอบข้</t>
-        </is>
+          <t xml:space="preserve">ตบนอกในบานตาย F7860</t>
+        </is>
+      </c>
+      <c r="D92">
+        <v>2.637</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">น้ำหนักที่ฝังในสูตร (ยังไม่ยืนยัน)</t>
+        </is>
+      </c>
+      <c r="G92">
+        <v>509</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">woodjamb</t>
+          <t xml:space="preserve">open_door</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t xml:space="preserve">JR01985</t>
+          <t xml:space="preserve">9014</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t xml:space="preserve">?</t>
+          <t xml:space="preserve">ตลาด</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t xml:space="preserve">กล่องเรียบ 1.6"×4" แนวตั้ง (ครอบข้</t>
+          <t xml:space="preserve">9014 คัลเทิลวอล — ตั้ง</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">woodjamb</t>
+          <t xml:space="preserve">fixed</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t xml:space="preserve">9014</t>
+          <t xml:space="preserve">กล่อง 1"x1.5"</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3727,19 +3727,30 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t xml:space="preserve">9014 คัลเทิลวอล — ตั้ง</t>
-        </is>
+          <t xml:space="preserve">ใบระแนง A (กล่อง 1×1.5″)</t>
+        </is>
+      </c>
+      <c r="D94">
+        <v>2.63</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">เมืองทอง · ไม่มี 1.5/1.2 → ใช้ NaN มม. (หนาสุดที่มี) ⚠</t>
+        </is>
+      </c>
+      <c r="G94">
+        <v>494</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">fixed</t>
+          <t xml:space="preserve">gate roof roof_gable</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">กล่อง 1"x1.5"</t>
+          <t xml:space="preserve">กล่อง 1x5</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3749,30 +3760,19 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t xml:space="preserve">ใบระแนง A (กล่อง 1×1.5″)</t>
-        </is>
-      </c>
-      <c r="D95">
-        <v>2.63</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">เมืองทอง · ไม่มี 1.5/1.2 → ใช้ NaN มม. (หนาสุดที่มี) ⚠</t>
-        </is>
-      </c>
-      <c r="G95">
-        <v>494</v>
+          <t xml:space="preserve">ใบระแนง A (กล่อง 1×5 ซม.)</t>
+        </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">gate roof roof_gable</t>
+          <t xml:space="preserve">gate</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">กล่อง 1x5</t>
+          <t xml:space="preserve">กล่อง 4 หุน</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3782,19 +3782,38 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t xml:space="preserve">ใบระแนง A (กล่อง 1×5 ซม.)</t>
+          <t xml:space="preserve">บังใบ 4 หุน</t>
+        </is>
+      </c>
+      <c r="D96">
+        <v>0.83</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S12071 12×12 หนา 1.2 (ไม่มี 1.5) · แคตตาล็อก Schimmer</t>
+        </is>
+      </c>
+      <c r="F96">
+        <v>170</v>
+      </c>
+      <c r="G96">
+        <v>156</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-8%</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">gate</t>
+          <t xml:space="preserve">slimlux</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t xml:space="preserve">กล่อง 4 หุน</t>
+          <t xml:space="preserve">แซด 4"</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3804,38 +3823,30 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve">บังใบ 4 หุน</t>
+          <t xml:space="preserve">แซด 4"</t>
         </is>
       </c>
       <c r="D97">
-        <v>0.83</v>
+        <v>3</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">S12071 12×12 หนา 1.2 (ไม่มี 1.5) · แคตตาล็อก Schimmer</t>
-        </is>
-      </c>
-      <c r="F97">
-        <v>170</v>
+          <t xml:space="preserve">น้ำหนักที่ฝังในสูตร (ยังไม่ยืนยัน)</t>
+        </is>
       </c>
       <c r="G97">
-        <v>156</v>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-8%</t>
-        </is>
+        <v>564</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">slimlux</t>
+          <t xml:space="preserve">roof</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t xml:space="preserve">แซด 4"</t>
+          <t xml:space="preserve">JR01679</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3845,30 +3856,38 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t xml:space="preserve">แซด 4"</t>
+          <t xml:space="preserve">เส้นคาดตาราง 2 ฝั่ง</t>
         </is>
       </c>
       <c r="D98">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">น้ำหนักที่ฝังในสูตร (ยังไม่ยืนยัน)</t>
-        </is>
+          <t xml:space="preserve">เจ้าของให้ 8 ต.ค.69 — เส้นคาดตาราง 0.40 กก./เส้น 6 ม.</t>
+        </is>
+      </c>
+      <c r="F98">
+        <v>140</v>
       </c>
       <c r="G98">
-        <v>564</v>
+        <v>75</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-46%</t>
+        </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">roof</t>
+          <t xml:space="preserve">bansolid</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t xml:space="preserve">JR01679</t>
+          <t xml:space="preserve">JR01822</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3878,22 +3897,30 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve">เส้นคาดตาราง 2 ฝั่ง</t>
-        </is>
-      </c>
-      <c r="F99">
-        <v>140</v>
+          <t xml:space="preserve">บังใบกล่อง ½"×1" แนวนอน (บน)</t>
+        </is>
+      </c>
+      <c r="D99">
+        <v>1.16</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">เมืองทอง · ไม่มี 1.5/1.2 → ใช้ NaN มม. (หนาสุดที่มี) ⚠</t>
+        </is>
+      </c>
+      <c r="G99">
+        <v>218</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">bansolid</t>
+          <t xml:space="preserve">woodjamb</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t xml:space="preserve">JR01822</t>
+          <t xml:space="preserve">JR01823</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3905,6 +3932,17 @@
         <is>
           <t xml:space="preserve">บังใบกล่อง ½"×1" แนวนอน (บน)</t>
         </is>
+      </c>
+      <c r="D100">
+        <v>1.16</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">เมืองทอง · ไม่มี 1.5/1.2 → ใช้ NaN มม. (หนาสุดที่มี) ⚠</t>
+        </is>
+      </c>
+      <c r="G100">
+        <v>218</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -3915,7 +3953,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t xml:space="preserve">JR01823</t>
+          <t xml:space="preserve">JR01984</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3925,7 +3963,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">บังใบกล่อง ½"×1" แนวนอน (บน)</t>
+          <t xml:space="preserve">กล่องเรียบ 1.6"×4" แนวตั้ง (ครอบข้</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -3937,7 +3975,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t xml:space="preserve">JR02944</t>
+          <t xml:space="preserve">JR01985</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3947,12 +3985,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve">ฉากข้อต่อ 2" (เฉพาะแปะนอก)</t>
+          <t xml:space="preserve">กล่องเรียบ 1.6"×4" แนวตั้ง (ครอบข้</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">gate</t>
+          <t xml:space="preserve">woodjamb</t>
         </is>
       </c>
     </row>
@@ -4160,7 +4198,7 @@
         </is>
       </c>
       <c r="D110">
-        <v>6.355</v>
+        <v>5.421</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -4168,7 +4206,7 @@
         </is>
       </c>
       <c r="G110">
-        <v>1195</v>
+        <v>1019</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
@@ -4603,7 +4641,7 @@
         </is>
       </c>
       <c r="D121">
-        <v>5.889</v>
+        <v>6.6</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4614,11 +4652,11 @@
         <v>1060</v>
       </c>
       <c r="G121">
-        <v>1107</v>
+        <v>1241</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">4%</t>
+          <t xml:space="preserve">17%</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -4726,7 +4764,7 @@
         </is>
       </c>
       <c r="D124">
-        <v>10.259</v>
+        <v>13.4</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4737,11 +4775,11 @@
         <v>2105</v>
       </c>
       <c r="G124">
-        <v>1929</v>
+        <v>2519</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">-8%</t>
+          <t xml:space="preserve">20%</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -4767,7 +4805,7 @@
         </is>
       </c>
       <c r="D125">
-        <v>1.779</v>
+        <v>2</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4778,11 +4816,11 @@
         <v>320</v>
       </c>
       <c r="G125">
-        <v>334</v>
+        <v>376</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">4%</t>
+          <t xml:space="preserve">18%</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -4849,7 +4887,7 @@
         </is>
       </c>
       <c r="D127">
-        <v>3.302</v>
+        <v>3.6</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -4860,11 +4898,11 @@
         <v>570</v>
       </c>
       <c r="G127">
-        <v>621</v>
+        <v>677</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">9%</t>
+          <t xml:space="preserve">19%</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -4890,7 +4928,7 @@
         </is>
       </c>
       <c r="D128">
-        <v>5.715</v>
+        <v>6.3</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -4901,11 +4939,11 @@
         <v>1000</v>
       </c>
       <c r="G128">
-        <v>1074</v>
+        <v>1184</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">7%</t>
+          <t xml:space="preserve">18%</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -4931,7 +4969,7 @@
         </is>
       </c>
       <c r="D129">
-        <v>1.504</v>
+        <v>1.75</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4942,11 +4980,11 @@
         <v>280</v>
       </c>
       <c r="G129">
-        <v>283</v>
+        <v>329</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">1%</t>
+          <t xml:space="preserve">18%</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -4972,7 +5010,7 @@
         </is>
       </c>
       <c r="D130">
-        <v>7.078</v>
+        <v>7.65</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -4983,11 +5021,11 @@
         <v>1210</v>
       </c>
       <c r="G130">
-        <v>1331</v>
+        <v>1438</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">10%</t>
+          <t xml:space="preserve">19%</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -5013,7 +5051,7 @@
         </is>
       </c>
       <c r="D131">
-        <v>1.478</v>
+        <v>1.65</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -5024,11 +5062,11 @@
         <v>265</v>
       </c>
       <c r="G131">
-        <v>278</v>
+        <v>310</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">5%</t>
+          <t xml:space="preserve">17%</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -5054,7 +5092,7 @@
         </is>
       </c>
       <c r="D132">
-        <v>1.446</v>
+        <v>1.7</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -5065,11 +5103,11 @@
         <v>270</v>
       </c>
       <c r="G132">
-        <v>272</v>
+        <v>320</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">1%</t>
+          <t xml:space="preserve">19%</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -5316,7 +5354,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E11"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -5389,7 +5427,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">JR01949</t>
+          <t xml:space="preserve">ฉาก 4"</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5443,7 +5481,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">JR02944</t>
+          <t xml:space="preserve">JR01984</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5453,7 +5491,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ฉากข้อต่อ 2" (เฉพาะแปะนอก)</t>
+          <t xml:space="preserve">กล่องเรียบ 1.6"×4" แนวตั้ง (ครอบข้</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -5463,14 +5501,14 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">gate</t>
+          <t xml:space="preserve">woodjamb</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">JR01679</t>
+          <t xml:space="preserve">JR01985</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5480,7 +5518,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">เส้นคาดตาราง 2 ฝั่ง</t>
+          <t xml:space="preserve">กล่องเรียบ 1.6"×4" แนวตั้ง (ครอบข้</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -5490,29 +5528,29 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">bansolid</t>
+          <t xml:space="preserve">woodjamb</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">JR01984</t>
+          <t xml:space="preserve">JR03130</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">?</t>
+          <t xml:space="preserve">market</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">กล่องเรียบ 1.6"×4" แนวตั้ง (ครอบข้</t>
+          <t xml:space="preserve">วงกบ/ธรณี มีติ่ง</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ยังไม่รู้แบรนด์</t>
+          <t xml:space="preserve">ไม่มีน้ำหนัก</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -5524,22 +5562,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">JR01985</t>
+          <t xml:space="preserve">JR03132</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">?</t>
+          <t xml:space="preserve">market</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">กล่องเรียบ 1.6"×4" แนวตั้ง (ครอบข้</t>
+          <t xml:space="preserve">กรอบบาน 3" มีบังใบ แนวตั้ง</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">ยังไม่รู้แบรนด์</t>
+          <t xml:space="preserve">ไม่มีน้ำหนัก</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -5551,7 +5589,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">JR01822</t>
+          <t xml:space="preserve">JR03131</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5561,7 +5599,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">บังใบกล่อง ½"×1" แนวนอน (บน)</t>
+          <t xml:space="preserve">กรอบบาน 3" มีบังใบ แนวตั้ง</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -5578,7 +5616,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">JR01823</t>
+          <t xml:space="preserve">JR03127</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5588,7 +5626,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">บังใบกล่อง ½"×1" แนวนอน (บน)</t>
+          <t xml:space="preserve">กรอบบาน 3" ไม่มีบังใบ แนวตั้ง</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -5602,122 +5640,14 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JR03130</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">market</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">วงกบ/ธรณี มีติ่ง</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ไม่มีน้ำหนัก</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">woodjamb</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JR03132</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">market</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">กรอบบาน 3" มีบังใบ แนวตั้ง</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ไม่มีน้ำหนัก</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">woodjamb</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JR03131</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">market</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">กรอบบาน 3" มีบังใบ แนวตั้ง</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ไม่มีน้ำหนัก</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">woodjamb</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JR03127</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">market</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">กรอบบาน 3" ไม่มีบังใบ แนวตั้ง</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ไม่มีน้ำหนัก</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">woodjamb</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:A15"/>
+  <autoFilter ref="A1:A11"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F26"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -6049,676 +5979,396 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">B24001</t>
+          <t xml:space="preserve">B20050</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">B24001 เฟรมบน</t>
+          <t xml:space="preserve">ตบปิดรางเตี้ย (งานใน)</t>
         </is>
       </c>
       <c r="C13">
-        <v>10.259</v>
+        <v>0.73</v>
       </c>
       <c r="D13">
-        <v>13.4</v>
+        <v>0.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">31%</t>
+          <t xml:space="preserve">23%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">folding</t>
+          <t xml:space="preserve">sms_slide bar_slide</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">B20050</t>
+          <t xml:space="preserve">F7986</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">ตบปิดรางเตี้ย (งานใน)</t>
+          <t xml:space="preserve">เดือย (ยูข้าง)</t>
         </is>
       </c>
       <c r="C14">
-        <v>0.73</v>
+        <v>1.37</v>
       </c>
       <c r="D14">
-        <v>0.9</v>
+        <v>1.65</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">23%</t>
+          <t xml:space="preserve">20%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">sms_slide bar_slide</t>
+          <t xml:space="preserve">euro_slide</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7986</t>
+          <t xml:space="preserve">B10004</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">เดือย (ยูข้าง)</t>
+          <t xml:space="preserve">เฟรมข้าง (NARROW FRAME)</t>
         </is>
       </c>
       <c r="C15">
-        <v>1.37</v>
+        <v>5.421</v>
       </c>
       <c r="D15">
-        <v>1.65</v>
+        <v>6.355</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">20%</t>
+          <t xml:space="preserve">17%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">euro_slide</t>
+          <t xml:space="preserve">banyok</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">B24009</t>
+          <t xml:space="preserve">B20001</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">B24009 ต่อกลาง</t>
+          <t xml:space="preserve">เฟรมบน</t>
         </is>
       </c>
       <c r="C16">
-        <v>1.446</v>
+        <v>7.104</v>
       </c>
       <c r="D16">
-        <v>1.7</v>
+        <v>8.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">18%</t>
+          <t xml:space="preserve">14%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">folding</t>
+          <t xml:space="preserve">sms_slide</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">B24006</t>
+          <t xml:space="preserve">F7992</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">B24006 บังใบข้าง</t>
+          <t xml:space="preserve">ตบปิดร่องบน (ตบกันสาด + ตัวปิด)</t>
         </is>
       </c>
       <c r="C17">
-        <v>1.504</v>
+        <v>2.694</v>
       </c>
       <c r="D17">
-        <v>1.75</v>
+        <v>2.95</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">16%</t>
+          <t xml:space="preserve">10%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">folding</t>
+          <t xml:space="preserve">euro_slide</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">B20001</t>
+          <t xml:space="preserve">F7943B</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">เฟรมบน</t>
+          <t xml:space="preserve">กรอบบาน เสา F7943B</t>
         </is>
       </c>
       <c r="C18">
-        <v>7.104</v>
+        <v>7.546</v>
       </c>
       <c r="D18">
-        <v>8.1</v>
+        <v>8.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">14%</t>
+          <t xml:space="preserve">10%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">sms_slide</t>
+          <t xml:space="preserve">awning</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">B20054</t>
+          <t xml:space="preserve">B20003</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ขวางบน/ล่าง</t>
+          <t xml:space="preserve">เฟรมข้าง</t>
         </is>
       </c>
       <c r="C19">
-        <v>5.889</v>
+        <v>6.029</v>
       </c>
       <c r="D19">
         <v>6.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">12%</t>
+          <t xml:space="preserve">9%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">sms_slide topslide pcdoor bar_slide</t>
+          <t xml:space="preserve">sms_slide</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">B24002</t>
+          <t xml:space="preserve">F7949</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">B24002 บังใบบน</t>
+          <t xml:space="preserve">คิ้วกระจก (ตั้ง)</t>
         </is>
       </c>
       <c r="C20">
-        <v>1.779</v>
+        <v>1.613</v>
       </c>
       <c r="D20">
-        <v>2</v>
+        <v>1.766</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">12%</t>
+          <t xml:space="preserve">9%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">folding</t>
+          <t xml:space="preserve">fold_euro</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">B24008</t>
+          <t xml:space="preserve">B20010</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">B24008 คิ้วตบกระจก แนวนอน</t>
+          <t xml:space="preserve">เสาเกี่ยวรับแรง</t>
         </is>
       </c>
       <c r="C21">
-        <v>1.478</v>
+        <v>7.27</v>
       </c>
       <c r="D21">
-        <v>1.65</v>
+        <v>7.8</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">12%</t>
+          <t xml:space="preserve">7%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">folding</t>
+          <t xml:space="preserve">sms_slide bar_slide</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7859</t>
+          <t xml:space="preserve">F7937</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">เฟรมข้าง F7859</t>
+          <t xml:space="preserve">เฟรมข้างช่องแสง F7937</t>
         </is>
       </c>
       <c r="C22">
-        <v>5.984</v>
+        <v>7.053</v>
       </c>
       <c r="D22">
-        <v>6.63</v>
+        <v>6.556</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">11%</t>
+          <t xml:space="preserve">-7%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">open_door awning pivot bansolid</t>
+          <t xml:space="preserve">open_door</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7992</t>
+          <t xml:space="preserve">B20041</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ตบปิดร่องบน (ตบกันสาด + ตัวปิด)</t>
+          <t xml:space="preserve">เฟรมล่างกันน้ำ (รางนอก)</t>
         </is>
       </c>
       <c r="C23">
-        <v>2.694</v>
+        <v>12.173</v>
       </c>
       <c r="D23">
-        <v>2.95</v>
+        <v>11.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">10%</t>
+          <t xml:space="preserve">-6%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">euro_slide</t>
+          <t xml:space="preserve">sms_slide bar_slide</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7939B</t>
+          <t xml:space="preserve">B20009</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">ธรณี F7939B</t>
+          <t xml:space="preserve">เสาเกี่ยวธรรมดา</t>
         </is>
       </c>
       <c r="C24">
-        <v>7.366</v>
+        <v>4.09</v>
       </c>
       <c r="D24">
-        <v>8.1</v>
+        <v>4.35</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">10%</t>
+          <t xml:space="preserve">6%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">awning</t>
+          <t xml:space="preserve">sms_slide topslide pcdoor bar_slide</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7943B</t>
+          <t xml:space="preserve">F7989</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">กรอบบาน เสา F7943B</t>
+          <t xml:space="preserve">ต่อเฟรมข้าง</t>
         </is>
       </c>
       <c r="C25">
-        <v>7.546</v>
+        <v>1.606</v>
       </c>
       <c r="D25">
-        <v>8.3</v>
+        <v>1.694</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">10%</t>
+          <t xml:space="preserve">5%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">awning</t>
+          <t xml:space="preserve">euro_slide</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">B24005</t>
+          <t xml:space="preserve">F7973</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">B24005 เฟรมข้าง</t>
+          <t xml:space="preserve">F7973 ตบปิดเฟรม (ตั้ง)</t>
         </is>
       </c>
       <c r="C26">
-        <v>5.715</v>
+        <v>1.216</v>
       </c>
       <c r="D26">
-        <v>6.3</v>
+        <v>1.278</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">10%</t>
+          <t xml:space="preserve">5%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">folding</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">B20003</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">เฟรมข้าง</t>
-        </is>
-      </c>
-      <c r="C27">
-        <v>6.029</v>
-      </c>
-      <c r="D27">
-        <v>6.6</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9%</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sms_slide</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">B24004</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">B24004 ตัวตับธรณี</t>
-        </is>
-      </c>
-      <c r="C28">
-        <v>3.302</v>
-      </c>
-      <c r="D28">
-        <v>3.6</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9%</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">folding</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">F7949</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">คิ้วกระจก (ตั้ง)</t>
-        </is>
-      </c>
-      <c r="C29">
-        <v>1.613</v>
-      </c>
-      <c r="D29">
-        <v>1.766</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9%</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fold_euro</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">B24007</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">B24007 ขวางบน+ล่าง</t>
-        </is>
-      </c>
-      <c r="C30">
-        <v>7.078</v>
-      </c>
-      <c r="D30">
-        <v>7.65</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8%</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">folding</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">B20010</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">เสาเกี่ยวรับแรง</t>
-        </is>
-      </c>
-      <c r="C31">
-        <v>7.27</v>
-      </c>
-      <c r="D31">
-        <v>7.8</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7%</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sms_slide bar_slide</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">F7937</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">เฟรมข้างช่องแสง F7937</t>
-        </is>
-      </c>
-      <c r="C32">
-        <v>7.053</v>
-      </c>
-      <c r="D32">
-        <v>6.556</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-7%</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">open_door</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">B20041</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">เฟรมล่างกันน้ำ (รางนอก)</t>
-        </is>
-      </c>
-      <c r="C33">
-        <v>12.173</v>
-      </c>
-      <c r="D33">
-        <v>11.5</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-6%</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sms_slide bar_slide</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">B20009</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">เสาเกี่ยวธรรมดา</t>
-        </is>
-      </c>
-      <c r="C34">
-        <v>4.09</v>
-      </c>
-      <c r="D34">
-        <v>4.35</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6%</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sms_slide topslide pcdoor bar_slide</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">F7989</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ต่อเฟรมข้าง</t>
-        </is>
-      </c>
-      <c r="C35">
-        <v>1.606</v>
-      </c>
-      <c r="D35">
-        <v>1.694</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5%</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">euro_slide</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">F7973</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">F7973 ตบปิดเฟรม (ตั้ง)</t>
-        </is>
-      </c>
-      <c r="C36">
-        <v>1.216</v>
-      </c>
-      <c r="D36">
-        <v>1.278</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5%</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
           <t xml:space="preserve">fold_euro fold_lift</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A36"/>
+  <autoFilter ref="A1:A26"/>
 </worksheet>
 </file>
--- a/docs/ราคาอลู-3แบรนด์-เทียบก่อนสลับ.xlsx
+++ b/docs/ราคาอลู-3แบรนด์-เทียบก่อนสลับ.xlsx
@@ -99,7 +99,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:M7"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -114,9 +114,6 @@
     <col min="11" max="11" width="13" customWidth="1"/>
     <col min="12" max="12" width="13" customWidth="1"/>
     <col min="13" max="13" width="13" customWidth="1"/>
-    <col min="14" max="14" width="13" customWidth="1"/>
-    <col min="15" max="15" width="13" customWidth="1"/>
-    <col min="16" max="16" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -139,70 +136,55 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">สีชุบขาว</t>
+          <t xml:space="preserve">อบขาว</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">สีชุบชา</t>
+          <t xml:space="preserve">ดำ</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">สีชุบดำ</t>
+          <t xml:space="preserve">เทาซาฮาร่า</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">อบขาว</t>
+          <t xml:space="preserve">ดำซาฮาร่า</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ดำ</t>
+          <t xml:space="preserve">แอทแทคเกรย์</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">เทาซาฮาร่า</t>
+          <t xml:space="preserve">ลายไม้สักทอง</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ดำซาฮาร่า</t>
+          <t xml:space="preserve">มะฮอกกานี</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve">แอทแทคเกรย์</t>
+          <t xml:space="preserve">ไวท์โอ๊ค</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ลายไม้สักทอง</t>
+          <t xml:space="preserve">มิว</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t xml:space="preserve">มะฮอกกานี</t>
+          <t xml:space="preserve">ขาว NA</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ไวท์โอ๊ค</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">มิว</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ขาว NA</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
         <is>
           <t xml:space="preserve">สีชา</t>
         </is>
@@ -216,51 +198,42 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">รหัสขึ้นต้น F ทุกตัว (บานเปิด/เฟี้ยม/เลื่อนยูโร · บานยก · กระทุ้ง) + ลูกฟูกทุกเส้น + กล่อง/ฉาก เฉพาะไซส์ในลิสต์</t>
+          <t xml:space="preserve">รหัสขึ้นต้น F ทุกตัว (บานเปิด/เฟี้ยม/เลื่อนยูโร · บานยก · กระทุ้ง) + ลูกฟูกทุกเส้น + กล่อง/ฉาก เฉพาะไซส์ในลิสต์ · ไม่มีสีชุบ/สีชา</t>
         </is>
       </c>
       <c r="C3">
         <v>193</v>
       </c>
       <c r="D3">
+        <v>193</v>
+      </c>
+      <c r="E3">
         <v>205</v>
       </c>
-      <c r="E3">
-        <v>208</v>
-      </c>
       <c r="F3">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="G3">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="H3">
-        <v>205</v>
+        <v>282</v>
       </c>
       <c r="I3">
-        <v>205</v>
+        <v>285</v>
       </c>
       <c r="J3">
-        <v>207</v>
+        <v>282</v>
       </c>
       <c r="K3">
-        <v>282</v>
-      </c>
-      <c r="L3">
-        <v>285</v>
-      </c>
-      <c r="M3">
-        <v>282</v>
-      </c>
-      <c r="N3">
         <v>182</v>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
@@ -277,60 +250,45 @@
           <t xml:space="preserve">รหัสขึ้นต้น B ทุกตัว (บานเลื่อน/เฟี้ยมเซมิยูโร) · ไม่มีลายไม้มะฮอกกานี/ไวท์โอ๊ค/แอทแทคเกรย์/สีชุบ</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4">
+        <v>188</v>
+      </c>
+      <c r="D4">
+        <v>188</v>
+      </c>
+      <c r="E4">
+        <v>203</v>
+      </c>
+      <c r="F4">
+        <v>203</v>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="H4">
+        <v>286</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="F4">
+      <c r="K4">
         <v>188</v>
       </c>
-      <c r="G4">
-        <v>188</v>
-      </c>
-      <c r="H4">
-        <v>203</v>
-      </c>
-      <c r="I4">
-        <v>203</v>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="K4">
-        <v>286</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
       <c r="M4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="N4">
-        <v>188</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
@@ -347,60 +305,45 @@
           <t xml:space="preserve">ตัว Z · กล่องที่มีชื่อเรียก (กล่องร่อง/กล่องเปิด) · กล่อง/ฉาก ไซส์นอกลิสต์ฟูจิ · วงกบมีติ่ง/กรอบบานเปิด 3" · ฉากข้อต่อ · ไม่มีลายไม้และแอทแทคเกรย์</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5">
+        <v>188</v>
+      </c>
+      <c r="D5">
+        <v>203</v>
+      </c>
+      <c r="E5">
+        <v>203</v>
+      </c>
+      <c r="F5">
+        <v>203</v>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="F5">
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="K5">
+        <v>183</v>
+      </c>
+      <c r="L5">
         <v>188</v>
       </c>
-      <c r="G5">
-        <v>203</v>
-      </c>
-      <c r="H5">
-        <v>203</v>
-      </c>
-      <c r="I5">
-        <v>203</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="N5">
-        <v>183</v>
-      </c>
-      <c r="O5">
-        <v>188</v>
-      </c>
-      <c r="P5">
+      <c r="M5">
         <v>198</v>
       </c>
     </row>

--- a/docs/ราคาอลู-3แบรนด์-เทียบก่อนสลับ.xlsx
+++ b/docs/ราคาอลู-3แบรนด์-เทียบก่อนสลับ.xlsx
@@ -1520,6 +1520,17 @@
           <t xml:space="preserve">ฉาก 4" ปิดราง</t>
         </is>
       </c>
+      <c r="D39">
+        <v>2.208</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">เจ้าของให้ 0.368 กก./ม. × 6 ม.</t>
+        </is>
+      </c>
+      <c r="G39">
+        <v>426</v>
+      </c>
       <c r="I39" t="inlineStr">
         <is>
           <t xml:space="preserve">topslide</t>
@@ -3651,6 +3662,17 @@
           <t xml:space="preserve">9014 คัลเทิลวอล — ตั้ง</t>
         </is>
       </c>
+      <c r="D93">
+        <v>3.396</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">เจ้าของให้ 0.566 กก./ม. × 6 ม.</t>
+        </is>
+      </c>
+      <c r="G93">
+        <v>638</v>
+      </c>
       <c r="I93" t="inlineStr">
         <is>
           <t xml:space="preserve">fixed</t>
@@ -3909,6 +3931,17 @@
           <t xml:space="preserve">กล่องเรียบ 1.6"×4" แนวตั้ง (ครอบข้</t>
         </is>
       </c>
+      <c r="D101">
+        <v>5.3</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">เจ้าของให้ 5.30 กก./เส้น 6 ม. (กล่องเรียบ 1.6"×4")</t>
+        </is>
+      </c>
+      <c r="G101">
+        <v>996</v>
+      </c>
       <c r="I101" t="inlineStr">
         <is>
           <t xml:space="preserve">woodjamb</t>
@@ -3930,6 +3963,17 @@
         <is>
           <t xml:space="preserve">กล่องเรียบ 1.6"×4" แนวตั้ง (ครอบข้</t>
         </is>
+      </c>
+      <c r="D102">
+        <v>5.3</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">เจ้าของให้ 5.30 กก./เส้น 6 ม. (กล่องเรียบ 1.6"×4")</t>
+        </is>
+      </c>
+      <c r="G102">
+        <v>996</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -5297,7 +5341,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E7"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -5343,7 +5387,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9014</t>
+          <t xml:space="preserve">กล่อง 1x5</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5353,7 +5397,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9014 คัลเทิลวอล — ตั้ง</t>
+          <t xml:space="preserve">ใบระแนง A (กล่อง 1×5 ซม.)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -5363,24 +5407,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">fixed</t>
+          <t xml:space="preserve">gate</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ฉาก 4"</t>
+          <t xml:space="preserve">JR03130</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuji</t>
+          <t xml:space="preserve">market</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ฉาก 4" ปิดราง</t>
+          <t xml:space="preserve">วงกบ/ธรณี มีติ่ง</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -5390,14 +5434,14 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">topslide</t>
+          <t xml:space="preserve">woodjamb</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">กล่อง 1x5</t>
+          <t xml:space="preserve">JR03132</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5407,7 +5451,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ใบระแนง A (กล่อง 1×5 ซม.)</t>
+          <t xml:space="preserve">กรอบบาน 3" มีบังใบ แนวตั้ง</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -5417,14 +5461,14 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">gate</t>
+          <t xml:space="preserve">woodjamb</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">JR01984</t>
+          <t xml:space="preserve">JR03131</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5434,7 +5478,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">กล่องเรียบ 1.6"×4" แนวตั้ง (ครอบข้</t>
+          <t xml:space="preserve">กรอบบาน 3" มีบังใบ แนวตั้ง</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -5451,7 +5495,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">JR01985</t>
+          <t xml:space="preserve">JR03127</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5461,7 +5505,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">กล่องเรียบ 1.6"×4" แนวตั้ง (ครอบข้</t>
+          <t xml:space="preserve">กรอบบาน 3" ไม่มีบังใบ แนวตั้ง</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -5475,116 +5519,8 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JR03130</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">market</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">วงกบ/ธรณี มีติ่ง</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ไม่มีน้ำหนัก</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">woodjamb</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JR03132</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">market</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">กรอบบาน 3" มีบังใบ แนวตั้ง</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ไม่มีน้ำหนัก</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">woodjamb</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JR03131</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">market</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">กรอบบาน 3" มีบังใบ แนวตั้ง</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ไม่มีน้ำหนัก</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">woodjamb</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JR03127</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">market</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">กรอบบาน 3" ไม่มีบังใบ แนวตั้ง</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ไม่มีน้ำหนัก</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">woodjamb</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:A11"/>
+  <autoFilter ref="A1:A7"/>
 </worksheet>
 </file>
 

--- a/docs/ราคาอลู-3แบรนด์-เทียบก่อนสลับ.xlsx
+++ b/docs/ราคาอลู-3แบรนด์-เทียบก่อนสลับ.xlsx
@@ -1224,15 +1224,15 @@
         </is>
       </c>
       <c r="D30">
-        <v>2.27</v>
+        <v>3.92</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">เมืองทอง · ไม่มี 1.5/1.2 → ใช้ NaN มม. (หนาสุดที่มี) ⚠</t>
+          <t xml:space="preserve">เมืองทอง · ไม่มี 1.5/1.2 → ใช้ 1.4 มม. (หนาสุดที่มี) ⚠</t>
         </is>
       </c>
       <c r="G30">
-        <v>438</v>
+        <v>757</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1323,15 +1323,15 @@
         </is>
       </c>
       <c r="D33">
-        <v>1.57</v>
+        <v>1.88</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">เมืองทอง · ไม่มี 1.5/1.2 → ใช้ NaN มม. (หนาสุดที่มี) ⚠</t>
+          <t xml:space="preserve">เมืองทอง · 1.2 มม. (ตามกฎ)</t>
         </is>
       </c>
       <c r="G33">
-        <v>303</v>
+        <v>363</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">เมืองทอง · ไม่มี 1.5/1.2 → ใช้ NaN มม. (หนาสุดที่มี) ⚠</t>
+          <t xml:space="preserve">เมืองทอง · ไม่มี 1.5/1.2 → ใช้ 1.1 มม. (หนาสุดที่มี) ⚠</t>
         </is>
       </c>
       <c r="G34">
@@ -1389,15 +1389,15 @@
         </is>
       </c>
       <c r="D35">
-        <v>4.86</v>
+        <v>6.05</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">เมืองทอง · ไม่มี 1.5/1.2 → ใช้ NaN มม. (หนาสุดที่มี) ⚠</t>
+          <t xml:space="preserve">เมืองทอง · 1.5 มม. (ตามกฎ)</t>
         </is>
       </c>
       <c r="G35">
-        <v>938</v>
+        <v>1168</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">เมืองทอง · ไม่มี 1.5/1.2 → ใช้ NaN มม. (หนาสุดที่มี) ⚠</t>
+          <t xml:space="preserve">เมืองทอง · 1.5 มม. (ตามกฎ)</t>
         </is>
       </c>
       <c r="G36">
@@ -3696,15 +3696,15 @@
         </is>
       </c>
       <c r="D94">
-        <v>2.63</v>
+        <v>1.99</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">เมืองทอง · ไม่มี 1.5/1.2 → ใช้ NaN มม. (หนาสุดที่มี) ⚠</t>
+          <t xml:space="preserve">เมืองทอง · ไม่มี 1.5/1.2 → ใช้ 1 มม. (หนาสุดที่มี) ⚠</t>
         </is>
       </c>
       <c r="G94">
-        <v>494</v>
+        <v>374</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -3792,15 +3792,15 @@
         </is>
       </c>
       <c r="D97">
-        <v>3</v>
+        <v>4.062</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">น้ำหนักที่ฝังในสูตร (ยังไม่ยืนยัน)</t>
+          <t xml:space="preserve">เมืองทอง · 1.5 มม. (ตามกฎ)</t>
         </is>
       </c>
       <c r="G97">
-        <v>564</v>
+        <v>764</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">เมืองทอง · ไม่มี 1.5/1.2 → ใช้ NaN มม. (หนาสุดที่มี) ⚠</t>
+          <t xml:space="preserve">เมืองทอง · ไม่มี 1.5/1.2 → ใช้ 1 มม. (หนาสุดที่มี) ⚠</t>
         </is>
       </c>
       <c r="G99">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">เมืองทอง · ไม่มี 1.5/1.2 → ใช้ NaN มม. (หนาสุดที่มี) ⚠</t>
+          <t xml:space="preserve">เมืองทอง · ไม่มี 1.5/1.2 → ใช้ 1 มม. (หนาสุดที่มี) ⚠</t>
         </is>
       </c>
       <c r="G100">

--- a/docs/ราคาอลู-3แบรนด์-เทียบก่อนสลับ.xlsx
+++ b/docs/ราคาอลู-3แบรนด์-เทียบก่อนสลับ.xlsx
@@ -3728,6 +3728,17 @@
           <t xml:space="preserve">ใบระแนง A (กล่อง 1×5 ซม.)</t>
         </is>
       </c>
+      <c r="D95">
+        <v>2.77</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">คำนวณ 10×50 มม. หนา 1.5 มม.</t>
+        </is>
+      </c>
+      <c r="G95">
+        <v>521</v>
+      </c>
       <c r="I95" t="inlineStr">
         <is>
           <t xml:space="preserve">gate</t>
@@ -5341,7 +5352,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E6"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -5387,7 +5398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">กล่อง 1x5</t>
+          <t xml:space="preserve">JR03130</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5397,7 +5408,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ใบระแนง A (กล่อง 1×5 ซม.)</t>
+          <t xml:space="preserve">วงกบ/ธรณี มีติ่ง</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -5407,14 +5418,14 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">gate</t>
+          <t xml:space="preserve">woodjamb</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">JR03130</t>
+          <t xml:space="preserve">JR03132</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5424,7 +5435,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">วงกบ/ธรณี มีติ่ง</t>
+          <t xml:space="preserve">กรอบบาน 3" มีบังใบ แนวตั้ง</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -5441,7 +5452,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">JR03132</t>
+          <t xml:space="preserve">JR03131</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5468,7 +5479,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">JR03131</t>
+          <t xml:space="preserve">JR03127</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5478,7 +5489,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">กรอบบาน 3" มีบังใบ แนวตั้ง</t>
+          <t xml:space="preserve">กรอบบาน 3" ไม่มีบังใบ แนวตั้ง</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -5492,35 +5503,8 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JR03127</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">market</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">กรอบบาน 3" ไม่มีบังใบ แนวตั้ง</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ไม่มีน้ำหนัก</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">woodjamb</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:A7"/>
+  <autoFilter ref="A1:A6"/>
 </worksheet>
 </file>
 

--- a/docs/ราคาอลู-3แบรนด์-เทียบก่อนสลับ.xlsx
+++ b/docs/ราคาอลู-3แบรนด์-เทียบก่อนสลับ.xlsx
@@ -2284,15 +2284,15 @@
         </is>
       </c>
       <c r="D58">
-        <v>7.778</v>
+        <v>7.366</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">น้ำหนักที่ฝังในสูตร (ยังไม่ยืนยัน)</t>
+          <t xml:space="preserve">แคตตาล็อก Euro Fuji รหัส F7939B</t>
         </is>
       </c>
       <c r="G58">
-        <v>1501</v>
+        <v>1422</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">น้ำหนักที่ฝังในสูตร (ยังไม่ยืนยัน)</t>
+          <t xml:space="preserve">แคตตาล็อก Euro Fuji รหัส F7943B</t>
         </is>
       </c>
       <c r="G60">

--- a/docs/ราคาอลู-3แบรนด์-เทียบก่อนสลับ.xlsx
+++ b/docs/ราคาอลู-3แบรนด์-เทียบก่อนสลับ.xlsx
@@ -3822,7 +3822,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t xml:space="preserve">JR01679</t>
+          <t xml:space="preserve">เส้นกลาง</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3840,19 +3840,11 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">เจ้าของให้ 8 ต.ค.69 — เส้นคาดตาราง 0.40 กก./เส้น 6 ม.</t>
-        </is>
-      </c>
-      <c r="F98">
-        <v>140</v>
+          <t xml:space="preserve">รหัสกลางของเส้นคาดตาราง — เจ้าของให้ 0.40 กก./เส้น 6 ม.</t>
+        </is>
       </c>
       <c r="G98">
         <v>75</v>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-46%</t>
-        </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>

--- a/docs/ราคาอลู-3แบรนด์-เทียบก่อนสลับ.xlsx
+++ b/docs/ราคาอลู-3แบรนด์-เทียบก่อนสลับ.xlsx
@@ -322,10 +322,8 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
+      <c r="H5">
+        <v>286</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>

--- a/docs/ราคาอลู-3แบรนด์-เทียบก่อนสลับ.xlsx
+++ b/docs/ราคาอลู-3แบรนด์-เทียบก่อนสลับ.xlsx
@@ -2430,15 +2430,15 @@
         </is>
       </c>
       <c r="D62">
-        <v>5</v>
+        <v>5.722</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">น้ำหนักที่ฝังในสูตร (ยังไม่ยืนยัน)</t>
+          <t xml:space="preserve">ชีตน้ำหนักโปรไฟล์ แถว 218 — F7944B 0.894 กก./ม. × 6.4 ม.</t>
         </is>
       </c>
       <c r="G62">
-        <v>965</v>
+        <v>1104</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3834,15 +3834,15 @@
         </is>
       </c>
       <c r="D98">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">รหัสกลางของเส้นคาดตาราง — เจ้าของให้ 0.40 กก./เส้น 6 ม.</t>
+          <t xml:space="preserve">รหัสกลางของเส้นคาดตาราง — เจ้าของให้ 0.8 กก./เส้น 6 ม.</t>
         </is>
       </c>
       <c r="G98">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>

--- a/docs/ราคาอลู-3แบรนด์-เทียบก่อนสลับ.xlsx
+++ b/docs/ราคาอลู-3แบรนด์-เทียบก่อนสลับ.xlsx
@@ -322,8 +322,10 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="H5">
-        <v>286</v>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
